--- a/Sample_run/1/student/hieunqhe171297/TC3/GradeDetail.xlsx
+++ b/Sample_run/1/student/hieunqhe171297/TC3/GradeDetail.xlsx
@@ -1056,7 +1056,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>48586</x:v>
+        <x:v>51622</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1451,7 +1451,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>48586</x:v>
+        <x:v>51622</x:v>
       </x:c>
       <x:c r="R9" s="4" t="s">
         <x:v>60</x:v>
